--- a/MainTop/07.06.2026 Макс ВБ/print_print_sorted.xlsx
+++ b/MainTop/07.06.2026 Макс ВБ/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\07.06.2026 Макс ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82CFDDD-1736-4750-8C46-473FC8007A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7609B314-5F4A-4D00-BCE3-2CEB7DE13B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -278,9 +278,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,37 +291,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor rgb="FFFFFF99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99CCFF"/>
+        <fgColor theme="8"/>
         <bgColor rgb="FF99CCFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
+        <fgColor theme="8"/>
         <bgColor rgb="FFFFCCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCFFCC"/>
+        <fgColor theme="8"/>
         <bgColor rgb="FFCCFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCCCFF"/>
+        <fgColor theme="6"/>
+        <bgColor rgb="FFCCFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFA07A"/>
+        <fgColor theme="6"/>
+        <bgColor rgb="FFFFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor rgb="FFFFA07A"/>
       </patternFill>
     </fill>
@@ -362,20 +388,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -678,10 +706,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.28515625" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="2" width="5.42578125" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -697,7 +729,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="1" t="s">
         <v>79</v>
       </c>
     </row>
@@ -714,7 +746,7 @@
       <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <f>B2/4</f>
         <v>18</v>
       </c>
@@ -732,7 +764,7 @@
       <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <f t="shared" ref="E3:E66" si="0">B3/4</f>
         <v>13</v>
       </c>
@@ -750,7 +782,7 @@
       <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -768,7 +800,7 @@
       <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -786,7 +818,7 @@
       <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -804,7 +836,7 @@
       <c r="D7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -822,1146 +854,1153 @@
       <c r="D8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>28</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9">
+      <c r="C9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>28</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10">
+      <c r="C10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>28</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11">
+      <c r="C11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>24</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12">
+      <c r="C12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>24</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13">
+      <c r="C13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>24</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14">
+      <c r="C14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>20</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15">
+      <c r="C15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>20</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16">
+      <c r="C16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>16</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17">
+      <c r="C17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18">
+      <c r="C18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="4">
         <v>16</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19">
+      <c r="C19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>16</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20">
+      <c r="C20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>16</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21">
+      <c r="C21" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>12</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22">
+      <c r="C22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>12</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23">
+      <c r="C23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="4">
         <v>8</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24">
+      <c r="C24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>8</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25">
+      <c r="C25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="4">
         <v>8</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26">
+      <c r="C26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="4">
         <v>8</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27">
+      <c r="C27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="4">
         <v>8</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E28">
+      <c r="C28" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="4">
         <v>4</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29">
+      <c r="C29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="4">
         <v>4</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E30">
+      <c r="C30" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="5">
         <v>4</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31">
+      <c r="C31" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="5">
         <v>4</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E32">
+      <c r="C32" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="5">
         <v>4</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33">
+      <c r="C33" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="5">
         <v>60</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E34">
+      <c r="C34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="5">
         <v>56</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E35">
+      <c r="C35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="5">
         <v>56</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E36">
+      <c r="C36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="5">
         <v>56</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37">
+      <c r="C37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="5">
         <v>40</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38">
+      <c r="C38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="5">
         <v>40</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39">
+      <c r="C39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="6">
         <v>40</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40">
+      <c r="C40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="6">
         <v>36</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E41">
+      <c r="C41" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="6">
         <v>36</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E42">
+      <c r="C42" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="6">
         <v>36</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E43">
+      <c r="C43" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="6">
         <v>32</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E44">
+      <c r="C44" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="6">
         <v>32</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E45">
+      <c r="C45" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="6">
         <v>28</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E46">
+      <c r="C46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E46" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47" s="6">
         <v>24</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E47">
+      <c r="C47" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E47" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48" s="6">
         <v>16</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E48">
+      <c r="C48" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49" s="7">
         <v>16</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E49">
+      <c r="C49" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="7">
         <v>12</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E50">
+      <c r="C50" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51" s="7">
         <v>12</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E51">
+      <c r="C51" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52" s="7">
         <v>12</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E52">
+      <c r="C52" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53" s="7">
         <v>12</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E53">
+      <c r="C53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E53" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B54" s="6">
+      <c r="B54" s="9">
         <v>8</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E54">
+      <c r="C54" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="8">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="9">
         <v>8</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E55">
+      <c r="C55" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E55" s="8">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="6">
+      <c r="B56" s="9">
         <v>8</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E56">
+      <c r="C56" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E56" s="8">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57" s="9">
         <v>8</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E57">
+      <c r="C57" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57" s="8">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B58" s="6">
+      <c r="B58" s="9">
         <v>4</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E58">
+      <c r="C58" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E58" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59" s="9">
         <v>4</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E59">
+      <c r="C59" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E59" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B60" s="6">
+      <c r="B60" s="9">
         <v>4</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E60">
+      <c r="C60" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B61" s="6">
+      <c r="B61" s="9">
         <v>4</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E61">
+      <c r="C61" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E61" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B62" s="6">
+      <c r="B62" s="9">
         <v>96</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E62">
+      <c r="D62" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E62" s="8">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B63" s="6">
+      <c r="B63" s="9">
         <v>92</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E63">
+      <c r="D63" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E63" s="8">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B64" s="6">
+      <c r="B64" s="9">
         <v>48</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E64">
+      <c r="D64" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E64" s="8">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B65" s="6">
+      <c r="B65" s="9">
         <v>20</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E65">
+      <c r="D65" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E65" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B66" s="6">
+      <c r="B66" s="9">
         <v>20</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E66">
+      <c r="D66" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E66" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="6">
+      <c r="B67" s="9">
         <v>12</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D67" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E67">
+      <c r="D67" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E67" s="8">
         <f t="shared" ref="E67:E71" si="1">B67/4</f>
         <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B68" s="6">
+      <c r="B68" s="9">
         <v>12</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E68">
+      <c r="D68" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E68" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="10">
         <v>8</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E69">
+      <c r="D69" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E69" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="10">
         <v>8</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E70">
+      <c r="D70" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E70" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
+      <c r="A71" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="11">
         <v>28</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D71" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E71">
+      <c r="D71" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E71" s="8">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E72" s="12">
+        <f>SUM(E2:E71)</f>
+        <v>436</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/MainTop/07.06.2026 Макс ВБ/print_print_sorted.xlsx
+++ b/MainTop/07.06.2026 Макс ВБ/print_print_sorted.xlsx
@@ -5,17 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\07.06.2026 Макс ВБ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\07.06.2026 Макс ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82CFDDD-1736-4750-8C46-473FC8007A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66979EB4-368B-4142-9FB2-ED6BEF32EEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -324,7 +335,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -358,24 +369,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -678,1290 +704,1297 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>72</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2">
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="4">
         <f>B2/4</f>
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>52</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3">
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="4">
         <f t="shared" ref="E3:E66" si="0">B3/4</f>
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>52</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4">
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>48</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5">
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>40</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6">
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>40</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7">
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>36</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8">
+      <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="5">
         <v>28</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9">
+      <c r="C9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="5">
         <v>28</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10">
+      <c r="C10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="5">
         <v>28</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11">
+      <c r="C11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="5">
         <v>24</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12">
+      <c r="C12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="5">
         <v>24</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13">
+      <c r="C13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="5">
         <v>24</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14">
+      <c r="C14" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="5">
         <v>20</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15">
+      <c r="C15" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="5">
         <v>20</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16">
+      <c r="C16" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="5">
         <v>16</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17">
+      <c r="C17" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="5">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18">
+      <c r="C18" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="5">
         <v>16</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19">
+      <c r="C19" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="5">
         <v>16</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20">
+      <c r="C20" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="5">
         <v>16</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21">
+      <c r="C21" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="5">
         <v>12</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22">
+      <c r="C22" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="5">
         <v>12</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23">
+      <c r="C23" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="5">
         <v>8</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24">
+      <c r="C24" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="5">
         <v>8</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25">
+      <c r="C25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="5">
         <v>8</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26">
+      <c r="C26" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="5">
         <v>8</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27">
+      <c r="C27" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="5">
         <v>8</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E28">
+      <c r="C28" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="5">
         <v>4</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29">
+      <c r="C29" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="5">
         <v>4</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E30">
+      <c r="C30" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="6">
         <v>4</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31">
+      <c r="C31" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="6">
         <v>4</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E32">
+      <c r="C32" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="6">
         <v>4</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33">
+      <c r="C33" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="6">
         <v>60</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E34">
+      <c r="C34" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="6">
         <v>56</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E35">
+      <c r="C35" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="6">
         <v>56</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E36">
+      <c r="C36" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="6">
         <v>56</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37">
+      <c r="C37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="6">
         <v>40</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38">
+      <c r="C38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="6">
         <v>40</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39">
+      <c r="C39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="7">
         <v>40</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40">
+      <c r="C40" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="7">
         <v>36</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E41">
+      <c r="C41" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="7">
         <v>36</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E42">
+      <c r="C42" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="7">
         <v>36</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E43">
+      <c r="C43" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="7">
         <v>32</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E44">
+      <c r="C44" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="7">
         <v>32</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E45">
+      <c r="C45" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="7">
         <v>28</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E46">
+      <c r="C46" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E46" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47" s="7">
         <v>24</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E47">
+      <c r="C47" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E47" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48" s="7">
         <v>16</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E48">
+      <c r="C48" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49" s="7">
         <v>16</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E49">
+      <c r="C49" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="7">
         <v>12</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E50">
+      <c r="C50" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51" s="7">
         <v>12</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E51">
+      <c r="C51" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52" s="7">
         <v>12</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E52">
+      <c r="C52" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53" s="7">
         <v>12</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E53">
+      <c r="C53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E53" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B54" s="6">
+      <c r="B54" s="8">
         <v>8</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E54">
+      <c r="C54" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="8">
         <v>8</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E55">
+      <c r="C55" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E55" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="6">
+      <c r="B56" s="8">
         <v>8</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E56">
+      <c r="C56" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E56" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57" s="8">
         <v>8</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E57">
+      <c r="C57" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B58" s="6">
+      <c r="B58" s="8">
         <v>4</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E58">
+      <c r="C58" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E58" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59" s="8">
         <v>4</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E59">
+      <c r="C59" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E59" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B60" s="6">
+      <c r="B60" s="8">
         <v>4</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E60">
+      <c r="C60" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B61" s="6">
+      <c r="B61" s="8">
         <v>4</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E61">
+      <c r="C61" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E61" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B62" s="6">
+      <c r="B62" s="8">
         <v>96</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E62">
+      <c r="D62" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E62" s="4">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B63" s="6">
+      <c r="B63" s="8">
         <v>92</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E63">
+      <c r="D63" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E63" s="4">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B64" s="6">
+      <c r="B64" s="8">
         <v>48</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E64">
+      <c r="D64" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E64" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B65" s="6">
+      <c r="B65" s="8">
         <v>20</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E65">
+      <c r="D65" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E65" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B66" s="6">
+      <c r="B66" s="8">
         <v>20</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E66">
+      <c r="D66" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E66" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="6">
+      <c r="B67" s="8">
         <v>12</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D67" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E67">
+      <c r="D67" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E67" s="4">
         <f t="shared" ref="E67:E71" si="1">B67/4</f>
         <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B68" s="6">
+      <c r="B68" s="8">
         <v>12</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E68">
+      <c r="D68" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E68" s="4">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="3">
         <v>8</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E69">
+      <c r="D69" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E69" s="4">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="3">
         <v>8</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E70">
+      <c r="D70" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E70" s="4">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
+      <c r="A71" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="9">
         <v>28</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D71" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E71">
+      <c r="D71" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E71" s="4">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E72" s="10">
+        <f>SUM(E2:E71)</f>
+        <v>436</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>